--- a/Compiled Data/merged_afm_data.xlsx
+++ b/Compiled Data/merged_afm_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liame\OneDrive\Documents\Summer26\Compiled Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A30601-8512-4D91-A1BC-96405F87627F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="5004" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="2376" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2228,6 +2228,21 @@
       <c r="AG16">
         <v>5</v>
       </c>
+      <c r="AH16">
+        <v>83</v>
+      </c>
+      <c r="AI16">
+        <v>66.452820000000003</v>
+      </c>
+      <c r="AJ16">
+        <v>11.363889</v>
+      </c>
+      <c r="AK16">
+        <v>52.519145000000002</v>
+      </c>
+      <c r="AL16">
+        <v>12.482900000000001</v>
+      </c>
       <c r="AM16" t="s">
         <v>43</v>
       </c>
@@ -2603,19 +2618,19 @@
         <v>5</v>
       </c>
       <c r="AH20">
-        <v>485</v>
+        <v>1591</v>
       </c>
       <c r="AI20">
-        <v>47.483289999999997</v>
+        <v>46.604171000000001</v>
       </c>
       <c r="AJ20">
-        <v>22.817260999999998</v>
+        <v>22.352616999999999</v>
       </c>
       <c r="AK20">
-        <v>28.739874</v>
+        <v>30.661078</v>
       </c>
       <c r="AL20">
-        <v>7.4740099999999998</v>
+        <v>8.8746360000000006</v>
       </c>
       <c r="AM20" t="s">
         <v>55</v>
@@ -2719,19 +2734,19 @@
         <v>5</v>
       </c>
       <c r="AH21">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="AI21">
-        <v>66.330046999999993</v>
+        <v>65.697034000000002</v>
       </c>
       <c r="AJ21">
-        <v>22.701340999999999</v>
+        <v>24.559342000000001</v>
       </c>
       <c r="AK21">
-        <v>43.266914</v>
+        <v>43.891061000000001</v>
       </c>
       <c r="AL21">
-        <v>13.636937</v>
+        <v>17.746853000000002</v>
       </c>
       <c r="AM21" t="s">
         <v>58</v>
@@ -2838,19 +2853,19 @@
         <v>5</v>
       </c>
       <c r="AH22">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="AI22">
-        <v>66.463432999999995</v>
+        <v>72.013481999999996</v>
       </c>
       <c r="AJ22">
-        <v>16.468640000000001</v>
+        <v>19.669703999999999</v>
       </c>
       <c r="AK22">
-        <v>46.929209</v>
+        <v>49.910642000000003</v>
       </c>
       <c r="AL22">
-        <v>10.723474</v>
+        <v>12.064560999999999</v>
       </c>
       <c r="AM22" t="s">
         <v>60</v>
@@ -2957,19 +2972,19 @@
         <v>5</v>
       </c>
       <c r="AH23">
-        <v>249</v>
+        <v>541</v>
       </c>
       <c r="AI23">
-        <v>48.365409</v>
+        <v>52.548602000000002</v>
       </c>
       <c r="AJ23">
-        <v>11.944312</v>
+        <v>12.889258999999999</v>
       </c>
       <c r="AK23">
-        <v>37.168567000000003</v>
+        <v>40.825097</v>
       </c>
       <c r="AL23">
-        <v>10.292017</v>
+        <v>10.910695</v>
       </c>
       <c r="AM23" t="s">
         <v>62</v>
@@ -3159,19 +3174,19 @@
         <v>5</v>
       </c>
       <c r="AH25">
-        <v>129</v>
+        <v>301</v>
       </c>
       <c r="AI25">
-        <v>57.931536000000001</v>
+        <v>61.088172</v>
       </c>
       <c r="AJ25">
-        <v>33.222607000000004</v>
+        <v>31.449728</v>
       </c>
       <c r="AK25">
-        <v>28.531451000000001</v>
+        <v>29.730820000000001</v>
       </c>
       <c r="AL25">
-        <v>13.54791</v>
+        <v>14.153563</v>
       </c>
       <c r="AM25" t="s">
         <v>66</v>
@@ -3269,19 +3284,19 @@
         <v>1</v>
       </c>
       <c r="AH26">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="AI26">
-        <v>17.737632999999999</v>
+        <v>18.140423999999999</v>
       </c>
       <c r="AJ26">
-        <v>4.8578270000000003</v>
+        <v>4.1810239999999999</v>
       </c>
       <c r="AK26">
-        <v>11.488168</v>
+        <v>12.879227</v>
       </c>
       <c r="AL26">
-        <v>3.2895799999999999</v>
+        <v>3.4861680000000002</v>
       </c>
       <c r="AM26" t="s">
         <v>76</v>
@@ -3379,19 +3394,19 @@
         <v>5</v>
       </c>
       <c r="AH27">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="AI27">
-        <v>84.215805000000003</v>
+        <v>84.411495000000002</v>
       </c>
       <c r="AJ27">
-        <v>15.553955</v>
+        <v>15.898616000000001</v>
       </c>
       <c r="AK27">
-        <v>65.719202999999993</v>
+        <v>65.211161000000004</v>
       </c>
       <c r="AL27">
-        <v>11.361672</v>
+        <v>11.567629</v>
       </c>
       <c r="AM27" t="s">
         <v>78</v>
@@ -3489,19 +3504,19 @@
         <v>5</v>
       </c>
       <c r="AH28">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="AI28">
-        <v>76.340303000000006</v>
+        <v>76.956812999999997</v>
       </c>
       <c r="AJ28">
-        <v>16.143633000000001</v>
+        <v>17.484394000000002</v>
       </c>
       <c r="AK28">
-        <v>57.693674999999999</v>
+        <v>56.911357000000002</v>
       </c>
       <c r="AL28">
-        <v>14.2493</v>
+        <v>14.818823</v>
       </c>
       <c r="AM28" t="s">
         <v>80</v>
@@ -3599,19 +3614,19 @@
         <v>5</v>
       </c>
       <c r="AH29">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI29">
-        <v>73.916116000000002</v>
+        <v>83.181245000000004</v>
       </c>
       <c r="AJ29">
-        <v>27.525880999999998</v>
+        <v>26.878205000000001</v>
       </c>
       <c r="AK29">
-        <v>37.274977</v>
+        <v>46.260160999999997</v>
       </c>
       <c r="AL29">
-        <v>15.739326</v>
+        <v>18.884641999999999</v>
       </c>
       <c r="AM29" t="s">
         <v>82</v>
@@ -3854,19 +3869,19 @@
         <v>5</v>
       </c>
       <c r="AH32">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="AI32">
-        <v>133.25214399999999</v>
+        <v>139.49566799999999</v>
       </c>
       <c r="AJ32">
-        <v>42.742758000000002</v>
+        <v>38.978067000000003</v>
       </c>
       <c r="AK32">
-        <v>43.650008</v>
+        <v>44.952212000000003</v>
       </c>
       <c r="AL32">
-        <v>11.897193</v>
+        <v>10.478723</v>
       </c>
       <c r="AM32" t="s">
         <v>91</v>

--- a/Compiled Data/merged_afm_data.xlsx
+++ b/Compiled Data/merged_afm_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liame\OneDrive\Documents\Summer26\Compiled Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7a53591c131afc/Documents/Summer26/Compiled Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9DAB63D-ED56-48F5-A8CA-4A8C88EA74D1}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2376" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="107">
   <si>
     <t>Sample ID</t>
   </si>
@@ -865,8 +865,8 @@
       <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
-        <v>24</v>
+      <c r="I2">
+        <v>0</v>
       </c>
       <c r="J2" t="s">
         <v>24</v>
@@ -951,8 +951,8 @@
       <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" t="s">
-        <v>24</v>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3" t="s">
         <v>24</v>
@@ -1043,8 +1043,8 @@
       <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
-        <v>24</v>
+      <c r="I4">
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
@@ -1129,8 +1129,8 @@
       <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
-        <v>24</v>
+      <c r="I5">
+        <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
@@ -1215,8 +1215,8 @@
       <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" t="s">
-        <v>24</v>
+      <c r="I6">
+        <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>24</v>
@@ -1307,8 +1307,8 @@
       <c r="H7" t="s">
         <v>24</v>
       </c>
-      <c r="I7" t="s">
-        <v>24</v>
+      <c r="I7">
+        <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>24</v>
@@ -1399,8 +1399,8 @@
       <c r="H8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" t="s">
-        <v>24</v>
+      <c r="I8">
+        <v>0</v>
       </c>
       <c r="J8" t="s">
         <v>24</v>
@@ -1491,8 +1491,8 @@
       <c r="H9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" t="s">
-        <v>24</v>
+      <c r="I9">
+        <v>0</v>
       </c>
       <c r="J9" t="s">
         <v>24</v>
@@ -1583,8 +1583,8 @@
       <c r="H10" t="s">
         <v>24</v>
       </c>
-      <c r="I10" t="s">
-        <v>24</v>
+      <c r="I10">
+        <v>0</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
@@ -1675,8 +1675,8 @@
       <c r="H11" t="s">
         <v>24</v>
       </c>
-      <c r="I11" t="s">
-        <v>24</v>
+      <c r="I11">
+        <v>0</v>
       </c>
       <c r="J11" t="s">
         <v>24</v>
@@ -1767,8 +1767,8 @@
       <c r="H12" t="s">
         <v>24</v>
       </c>
-      <c r="I12" t="s">
-        <v>24</v>
+      <c r="I12">
+        <v>0</v>
       </c>
       <c r="J12" t="s">
         <v>24</v>

--- a/Compiled Data/merged_afm_data.xlsx
+++ b/Compiled Data/merged_afm_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7a53591c131afc/Documents/Summer26/Compiled Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9DAB63D-ED56-48F5-A8CA-4A8C88EA74D1}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1354B60-D133-48A6-82B1-F5ECB73C41E1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="107">
   <si>
     <t>Sample ID</t>
   </si>
@@ -3253,6 +3253,12 @@
       <c r="T26" t="s">
         <v>77</v>
       </c>
+      <c r="U26">
+        <v>3.0013809999999999</v>
+      </c>
+      <c r="V26">
+        <v>8.5244E-2</v>
+      </c>
       <c r="W26">
         <v>106</v>
       </c>
@@ -3273,6 +3279,9 @@
       </c>
       <c r="AC26">
         <v>1.1559090000000001</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>70</v>
       </c>
       <c r="AE26" t="s">
         <v>74</v>
@@ -3363,6 +3372,12 @@
       <c r="T27" t="s">
         <v>79</v>
       </c>
+      <c r="U27">
+        <v>6.0826710000000004</v>
+      </c>
+      <c r="V27">
+        <v>2.0291320000000002</v>
+      </c>
       <c r="W27">
         <v>164</v>
       </c>
@@ -3383,6 +3398,9 @@
       </c>
       <c r="AC27">
         <v>5.2805369999999998</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>71</v>
       </c>
       <c r="AE27" t="s">
         <v>73</v>
@@ -3473,6 +3491,12 @@
       <c r="T28" t="s">
         <v>81</v>
       </c>
+      <c r="U28">
+        <v>6.5698030000000003</v>
+      </c>
+      <c r="V28">
+        <v>2.2874569999999999</v>
+      </c>
       <c r="W28">
         <v>463</v>
       </c>
@@ -3493,6 +3517,9 @@
       </c>
       <c r="AC28">
         <v>5.1421419999999998</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>71</v>
       </c>
       <c r="AE28" t="s">
         <v>73</v>
@@ -3583,6 +3610,12 @@
       <c r="T29" t="s">
         <v>84</v>
       </c>
+      <c r="U29">
+        <v>2.9997929999999999</v>
+      </c>
+      <c r="V29">
+        <v>8.7859000000000007E-2</v>
+      </c>
       <c r="W29">
         <v>28</v>
       </c>
@@ -3603,6 +3636,9 @@
       </c>
       <c r="AC29">
         <v>4.6952769999999999</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>70</v>
       </c>
       <c r="AE29" t="s">
         <v>73</v>
@@ -3693,6 +3729,15 @@
       <c r="T30" t="s">
         <v>87</v>
       </c>
+      <c r="U30">
+        <v>5.332217</v>
+      </c>
+      <c r="V30">
+        <v>0.92325500000000005</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>71</v>
+      </c>
       <c r="AE30" t="s">
         <v>70</v>
       </c>
@@ -3767,6 +3812,15 @@
       <c r="T31" t="s">
         <v>90</v>
       </c>
+      <c r="U31">
+        <v>3.9894880000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.41426800000000003</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>71</v>
+      </c>
       <c r="AE31" t="s">
         <v>70</v>
       </c>
@@ -3838,6 +3892,12 @@
       <c r="S32" s="3">
         <v>8.4000000000000005E-2</v>
       </c>
+      <c r="U32">
+        <v>4.6798679999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.96627300000000005</v>
+      </c>
       <c r="W32">
         <v>58</v>
       </c>
@@ -3858,6 +3918,9 @@
       </c>
       <c r="AC32">
         <v>3.6822520000000001</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>71</v>
       </c>
       <c r="AE32" t="s">
         <v>73</v>

--- a/Compiled Data/merged_afm_data.xlsx
+++ b/Compiled Data/merged_afm_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7a53591c131afc/Documents/Summer26/Compiled Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1354B60-D133-48A6-82B1-F5ECB73C41E1}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D7B69F-A3FB-4DFE-97A0-5EE2D3880172}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -411,6 +411,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -914,7 +918,7 @@
         <v>0.86092000000000002</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AE2" t="s">
         <v>73</v>
@@ -1092,7 +1096,7 @@
         <v>0.74989099999999997</v>
       </c>
       <c r="AD4" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AE4" t="s">
         <v>73</v>
@@ -1178,7 +1182,7 @@
         <v>0.90149299999999999</v>
       </c>
       <c r="AD5" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AE5" t="s">
         <v>74</v>

--- a/Compiled Data/merged_afm_data.xlsx
+++ b/Compiled Data/merged_afm_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7a53591c131afc/Documents/Summer26/Compiled Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D7B69F-A3FB-4DFE-97A0-5EE2D3880172}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{1EEBAEA9-F0AA-4535-B607-163CF9D1A63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C4B7C5-6EE9-47DE-AB75-3500768EC5D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="108">
   <si>
     <t>Sample ID</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>SEM # of features</t>
+  </si>
+  <si>
+    <t># of SEM Scans</t>
   </si>
 </sst>
 </file>
@@ -702,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -725,10 +728,10 @@
     <col min="27" max="29" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="15.44140625" customWidth="1"/>
     <col min="35" max="35" width="15.44140625" customWidth="1"/>
-    <col min="39" max="39" width="15.44140625" customWidth="1"/>
+    <col min="40" max="40" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -844,10 +847,13 @@
         <v>103</v>
       </c>
       <c r="AM1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -929,11 +935,11 @@
       <c r="AG2">
         <v>5</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1021,11 +1027,11 @@
       <c r="AG3">
         <v>5</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1107,11 +1113,11 @@
       <c r="AG4">
         <v>5</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1193,11 +1199,11 @@
       <c r="AG5">
         <v>5</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1285,11 +1291,11 @@
       <c r="AG6">
         <v>5</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1377,11 +1383,11 @@
       <c r="AG7">
         <v>5</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1469,11 +1475,11 @@
       <c r="AG8">
         <v>5</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AN8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1561,11 +1567,11 @@
       <c r="AG9">
         <v>3</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AN9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1653,11 +1659,11 @@
       <c r="AG10">
         <v>5</v>
       </c>
-      <c r="AM10" t="s">
+      <c r="AN10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1745,11 +1751,11 @@
       <c r="AG11">
         <v>5</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AN11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1837,11 +1843,11 @@
       <c r="AG12">
         <v>5</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AN12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1926,11 +1932,11 @@
       <c r="AG13">
         <v>5</v>
       </c>
-      <c r="AM13" t="s">
+      <c r="AN13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2009,11 +2015,11 @@
       <c r="AG14" t="s">
         <v>94</v>
       </c>
-      <c r="AM14" t="s">
+      <c r="AN14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2128,11 +2134,14 @@
       <c r="AL15">
         <v>11.564944000000001</v>
       </c>
-      <c r="AM15" t="s">
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -2247,11 +2256,14 @@
       <c r="AL16">
         <v>12.482900000000001</v>
       </c>
-      <c r="AM16" t="s">
+      <c r="AM16">
+        <v>3</v>
+      </c>
+      <c r="AN16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -2330,11 +2342,11 @@
       <c r="AG17" t="s">
         <v>94</v>
       </c>
-      <c r="AM17" t="s">
+      <c r="AN17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -2434,11 +2446,11 @@
       <c r="AG18">
         <v>5</v>
       </c>
-      <c r="AM18" t="s">
+      <c r="AN18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -2517,11 +2529,11 @@
       <c r="AG19" t="s">
         <v>94</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="AN19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2636,11 +2648,14 @@
       <c r="AL20">
         <v>8.8746360000000006</v>
       </c>
-      <c r="AM20" t="s">
+      <c r="AM20">
+        <v>3</v>
+      </c>
+      <c r="AN20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -2752,11 +2767,14 @@
       <c r="AL21">
         <v>17.746853000000002</v>
       </c>
-      <c r="AM21" t="s">
+      <c r="AM21">
+        <v>3</v>
+      </c>
+      <c r="AN21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -2871,11 +2889,14 @@
       <c r="AL22">
         <v>12.064560999999999</v>
       </c>
-      <c r="AM22" t="s">
+      <c r="AM22">
+        <v>3</v>
+      </c>
+      <c r="AN22" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -2990,11 +3011,14 @@
       <c r="AL23">
         <v>10.910695</v>
       </c>
-      <c r="AM23" t="s">
+      <c r="AM23">
+        <v>3</v>
+      </c>
+      <c r="AN23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -3073,11 +3097,11 @@
       <c r="AG24" t="s">
         <v>94</v>
       </c>
-      <c r="AM24" t="s">
+      <c r="AN24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -3192,11 +3216,14 @@
       <c r="AL25">
         <v>14.153563</v>
       </c>
-      <c r="AM25" t="s">
+      <c r="AM25">
+        <v>3</v>
+      </c>
+      <c r="AN25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -3311,11 +3338,11 @@
       <c r="AL26">
         <v>3.4861680000000002</v>
       </c>
-      <c r="AM26" t="s">
+      <c r="AN26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3430,11 +3457,14 @@
       <c r="AL27">
         <v>11.567629</v>
       </c>
-      <c r="AM27" t="s">
+      <c r="AM27">
+        <v>3</v>
+      </c>
+      <c r="AN27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -3549,11 +3579,14 @@
       <c r="AL28">
         <v>14.818823</v>
       </c>
-      <c r="AM28" t="s">
+      <c r="AM28">
+        <v>3</v>
+      </c>
+      <c r="AN28" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -3668,11 +3701,14 @@
       <c r="AL29">
         <v>18.884641999999999</v>
       </c>
-      <c r="AM29" t="s">
+      <c r="AM29">
+        <v>3</v>
+      </c>
+      <c r="AN29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -3751,11 +3787,11 @@
       <c r="AG30" t="s">
         <v>94</v>
       </c>
-      <c r="AM30" t="s">
+      <c r="AN30" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -3834,11 +3870,11 @@
       <c r="AG31" t="s">
         <v>94</v>
       </c>
-      <c r="AM31" t="s">
+      <c r="AN31" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -3950,7 +3986,10 @@
       <c r="AL32">
         <v>10.478723</v>
       </c>
-      <c r="AM32" t="s">
+      <c r="AM32">
+        <v>3</v>
+      </c>
+      <c r="AN32" t="s">
         <v>91</v>
       </c>
     </row>
